--- a/human_resources_forms/047_whc_application_form--human_resources_forms.xlsx
+++ b/human_resources_forms/047_whc_application_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'less_than_1_year',_'label':_'less_than_1_year'}</t>
+          <t>less_than_1_year</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'Less than 1 year', 'label': 'Less than 1 year'}</t>
+          <t>Less than 1 year</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'1-2_years',_'label':_'1-2_years'}</t>
+          <t>1-2_years</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': '1-2 years', 'label': '1-2 years'}</t>
+          <t>1-2 years</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'2-5_years',_'label':_'2-5_years'}</t>
+          <t>2-5_years</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': '2-5 years', 'label': '2-5 years'}</t>
+          <t>2-5 years</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'more_than_5_years',_'label':_'more_than_5_years'}</t>
+          <t>more_than_5_years</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'More than 5 years', 'label': 'More than 5 years'}</t>
+          <t>More than 5 years</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'Active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'Inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'on_vacation',_'label':_'on_vacation'}</t>
+          <t>on_vacation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'On vacation', 'label': 'On vacation'}</t>
+          <t>On vacation</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_25,_'name':_'on_leave',_'label':_'on_leave'}</t>
+          <t>on_leave</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 25, 'name': 'On leave', 'label': 'On leave'}</t>
+          <t>On leave</t>
         </is>
       </c>
     </row>
